--- a/call_report_preliminary_analysis.xlsx
+++ b/call_report_preliminary_analysis.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purpose &amp; Endeavor Link" sheetId="1" r:id="R9a465b7708624fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="2" r:id="Rdf3cebf699794ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robustness Check" sheetId="3" r:id="R656ca6a7b1794d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Findings" sheetId="4" r:id="R368c0e3f2cd346f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Roadmap" sheetId="5" r:id="R43f7c72b622749b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="6" r:id="Rd351839be11f405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failed Bank Profiles" sheetId="7" r:id="R55c159e59d1d4b50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal Comparison" sheetId="8" r:id="Rc9befc4248584ce1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohort Summary" sheetId="9" r:id="Rf1fc4ca096574088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Metrics" sheetId="10" r:id="R6e3b9af9426f4bb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight Sensitivity" sheetId="11" r:id="Rb870d147f5ed44c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macro Context" sheetId="12" r:id="R3a1ea72e43244127"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" r:id="R672018f9ccbb4461"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" r:id="R20a00c24bc364afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purpose &amp; Endeavor Link" sheetId="1" r:id="R8e467e260d124ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="2" r:id="R2e95fb2f8b2c4988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Robustness Check" sheetId="3" r:id="R02da1686874d40b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Findings" sheetId="4" r:id="R410b9bb72079406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Roadmap" sheetId="5" r:id="R10790eb1b12f48fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Milestones" sheetId="6" r:id="R8b8c577a661043fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failed Bank Profiles" sheetId="7" r:id="R4aee0d79f8114b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signal Comparison" sheetId="8" r:id="R4daef21afa0446cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohort Summary" sheetId="9" r:id="Rb0d51e9de4354b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Metrics" sheetId="10" r:id="R4365f55ec57545a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight Sensitivity" sheetId="11" r:id="Rb67fd37bb0614932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macro Context" sheetId="12" r:id="Rb30363fdcdf548a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" r:id="Rcb28d4b0078a45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" r:id="Ra3b49442ce524a53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -137,100 +137,7 @@
     <x:t xml:space="preserve">Verifiable evidence</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">1. Validate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q1 2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Freeze and pre-register version 1.0 specification</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Specification document</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OSF or Zenodo timestamp</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Planned</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q1 to Q2 2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Build quarterly bank panel (2001 to latest) from Call Reports; add FRED macro series</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reproducible data pipeline</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Repository release</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q2 to Q4 2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Run tests T2 to T5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Validation results report</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Public report with all results, including failures</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2. Share findings</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q3 2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Working paper</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Paper posted on SSRN</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SSRN posting date and download count</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q4 2027 to Q2 2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Present to practitioners and researchers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Talks, e.g., GARP chapter, a state bankers association, the Federal Reserve and CSBS Community Banking research conference</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Invitations, programs, attendee counts</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q1 2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Submit to a peer-reviewed journal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Submission, e.g., Journal of Risk Model Validation or Journal of Financial Stability</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Submission confirmation; reviewer feedback</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">3. Tools</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Q2 to Q4 2028</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Extend to $1bn to $10bn banks (T6); release a bank self-assessment template</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Excel and Python template with user guide</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Downloads; feedback from banks</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Q4 2028</x:t>
@@ -243,6 +150,9 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Public release</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Planned</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">4. Training and upkeep</x:t>
@@ -425,9 +335,6 @@
     <x:t xml:space="preserve">15% rate + 25% funding + 5% credit + 5% capital + 20% interaction + 30% trigger</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">In-sample hypothesis that must be frozen before out-of-time testing.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Limitations that must remain visible</x:t>
   </x:si>
   <x:si>
@@ -470,7 +377,7 @@
     <x:numFmt numFmtId="171" formatCode="0.00%"/>
     <x:numFmt numFmtId="172" formatCode="0.000"/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial"/>
@@ -603,8 +510,25 @@
       <x:color rgb="FF2F75B5"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF27632A"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFC23B44"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF27632A"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -659,6 +583,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -946,7 +875,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="127">
+  <x:cellXfs count="135">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -1393,6 +1322,30 @@
     </x:xf>
     <x:xf numFmtId="172" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="24" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="7">
@@ -2290,7 +2243,7 @@
         <x:color rgb="FFB23A48"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3057,7 +3010,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref4d1e47eb4c480c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R917833dd209846aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3092,7 +3045,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0b18250472af4824"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd545e65fb9ab4728"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3491,17 +3444,17 @@
       </x:c>
       <x:c r="D10" s="7"/>
     </x:row>
-    <x:row r="11" ht="57.75" hidden="0" customHeight="1">
+    <x:row r="11" ht="72" hidden="0" customHeight="1">
       <x:c r="A11" s="120" t="str">
         <x:v>A testable next step</x:v>
       </x:c>
       <x:c r="B11" s="77" t="str">
-        <x:v>The specification will be frozen before a credit-driven 2008-2011 test and evaluated against stated success criteria.</x:v>
+        <x:v>Version 1.0.1 was frozen and independently timestamped on October 8, 2026 (https://doi.org/10.5281/zenodo.23246551). The unchanged specification will be evaluated in the 2008-2011 and 2019-2020 historical tests and in a prospective test.</x:v>
       </x:c>
       <x:c r="C11" s="77" t="str">
         <x:v>See Validation Roadmap and Milestones.</x:v>
       </x:c>
-      <x:c r="D11" s="7"/>
+      <x:c r="D11" s="77"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0">
       <x:c r="A13" s="4" t="s">
@@ -3577,15 +3530,15 @@
         <x:v>Reproducible source record</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="43.5" hidden="0" customHeight="1">
+    <x:row r="21" ht="24" hidden="0" customHeight="1">
       <x:c r="A21" s="77" t="str">
         <x:v>Public code repository</x:v>
       </x:c>
       <x:c r="B21" s="77" t="str">
-        <x:v>Not yet created</x:v>
+        <x:v>Completed - version 1.0.1 released October 8, 2026</x:v>
       </x:c>
       <x:c r="C21" s="77" t="str">
-        <x:v>Publish a dated release and archive it for a DOI</x:v>
+        <x:v>Maintain versioned releases and the DOI archive (https://doi.org/10.5281/zenodo.23246551)</x:v>
       </x:c>
       <x:c r="D21" s="77" t="str">
         <x:v>Independent timestamp and version history</x:v>
@@ -13044,7 +12997,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4442c8fb3644002"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fca1db1e57a4c3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13062,7 +13015,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>88</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -13071,7 +13024,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>89</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -13357,7 +13310,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc20560fb1ba245c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa2f1c47509f40f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13375,7 +13328,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -13383,7 +13336,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>91</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -13577,9 +13530,9 @@
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07a214a87a6842b7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf68da80d99f948d4"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R619a93f70d5d44d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R838a9142de304e99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13599,7 +13552,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>92</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -13607,7 +13560,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>93</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -13615,161 +13568,161 @@
     </x:row>
     <x:row r="4" ht="30" hidden="0" customHeight="1">
       <x:c r="A4" s="32" t="s">
-        <x:v>94</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="32" t="s">
-        <x:v>95</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C4" s="32" t="s">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="32" t="s">
-        <x:v>97</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" hidden="0" customHeight="1">
       <x:c r="A5" s="39" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B5" s="39" t="s">
-        <x:v>99</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="39" t="s">
-        <x:v>100</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D5" s="39" t="s">
-        <x:v>101</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" hidden="0" customHeight="1">
       <x:c r="A6" s="39" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="39" t="s">
-        <x:v>102</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="39" t="s">
-        <x:v>103</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D6" s="39" t="s">
-        <x:v>104</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" hidden="0" customHeight="1">
       <x:c r="A7" s="39" t="s">
-        <x:v>105</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B7" s="39" t="s">
-        <x:v>106</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C7" s="39" t="s">
-        <x:v>107</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D7" s="39" t="s">
-        <x:v>108</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" hidden="0" customHeight="1">
       <x:c r="A8" s="39" t="s">
-        <x:v>105</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B8" s="39" t="s">
-        <x:v>109</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="39" t="s">
-        <x:v>110</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D8" s="39" t="s">
-        <x:v>111</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" hidden="0" customHeight="1">
       <x:c r="A9" s="39" t="s">
-        <x:v>112</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" s="39" t="s">
-        <x:v>113</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="39" t="s">
-        <x:v>114</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D9" s="39" t="s">
-        <x:v>115</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" hidden="0" customHeight="1">
       <x:c r="A10" s="39" t="s">
-        <x:v>112</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="39" t="s">
-        <x:v>116</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C10" s="39" t="s">
-        <x:v>117</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D10" s="39" t="s">
-        <x:v>118</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" hidden="0" customHeight="1">
       <x:c r="A11" s="39" t="s">
-        <x:v>119</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B11" s="39" t="s">
-        <x:v>120</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C11" s="39" t="s">
-        <x:v>121</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D11" s="39" t="s">
-        <x:v>122</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" hidden="0" customHeight="1">
       <x:c r="A12" s="39" t="s">
-        <x:v>123</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="39" t="s">
-        <x:v>124</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C12" s="39" t="s">
-        <x:v>125</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="39" t="s">
-        <x:v>126</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" hidden="0" customHeight="1">
       <x:c r="A13" s="39" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B13" s="39" t="s">
-        <x:v>128</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C13" s="39" t="s">
-        <x:v>129</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D13" s="39" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="42" hidden="0" customHeight="1">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" hidden="0" customHeight="1">
       <x:c r="A14" s="39" t="s">
-        <x:v>131</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B14" s="39" t="s">
-        <x:v>132</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C14" s="39" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="D14" s="39" t="s">
-        <x:v>134</x:v>
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D14" s="134" t="str">
+        <x:v>In-sample hypothesis frozen as version 1.0.1 before locked-specification historical and prospective testing.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0">
       <x:c r="A17" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B17" s="11"/>
       <x:c r="C17" s="11"/>
@@ -13780,7 +13733,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B18" s="39" t="s">
-        <x:v>136</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C18" s="39"/>
       <x:c r="D18" s="39"/>
@@ -13790,7 +13743,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="39" t="s">
-        <x:v>137</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C19" s="39"/>
       <x:c r="D19" s="39"/>
@@ -13800,7 +13753,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B20" s="39" t="s">
-        <x:v>138</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C20" s="39"/>
       <x:c r="D20" s="39"/>
@@ -13810,7 +13763,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B21" s="39" t="s">
-        <x:v>139</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C21" s="39"/>
       <x:c r="D21" s="39"/>
@@ -13820,7 +13773,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B22" s="39" t="s">
-        <x:v>140</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C22" s="39"/>
       <x:c r="D22" s="39"/>
@@ -13830,7 +13783,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B23" s="39" t="s">
-        <x:v>141</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C23" s="39"/>
       <x:c r="D23" s="39"/>
@@ -13876,7 +13829,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>142</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -13884,7 +13837,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>143</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -13982,7 +13935,7 @@
         <x:v>Reproducibility</x:v>
       </x:c>
       <x:c r="C10" s="123" t="str">
-        <x:v>call_report_v3_support/data/raw/fdic_financials_2022q4.json</x:v>
+        <x:v>data/raw/fdic_financials_2022q4.json</x:v>
       </x:c>
       <x:c r="D10" s="123" t="str">
         <x:v>Included with the workbook.</x:v>
@@ -13996,7 +13949,7 @@
         <x:v>Reproducibility</x:v>
       </x:c>
       <x:c r="C11" s="123" t="str">
-        <x:v>call_report_v3_support/data/raw/fdic_failures_2023.json</x:v>
+        <x:v>data/raw/fdic_failures_2023.json</x:v>
       </x:c>
       <x:c r="D11" s="123" t="str">
         <x:v>Included with the workbook.</x:v>
@@ -14010,24 +13963,24 @@
         <x:v>Macroeconomic context</x:v>
       </x:c>
       <x:c r="C12" s="123" t="str">
-        <x:v>call_report_v3_support/data/raw/fred_dff.csv and fred_dgs10.csv</x:v>
+        <x:v>data/raw/fred_dff.csv and data/raw/fred_dgs10.csv</x:v>
       </x:c>
       <x:c r="D12" s="123" t="str">
         <x:v>Included with the workbook.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="38" customHeight="1">
-      <x:c r="A13" s="124" t="str">
-        <x:v>Analysis code</x:v>
-      </x:c>
-      <x:c r="B13" s="124" t="str">
-        <x:v>Sample filter, formulas, and outputs</x:v>
-      </x:c>
-      <x:c r="C13" s="124" t="str">
-        <x:v>call_report_v3_support/analysis.py</x:v>
-      </x:c>
-      <x:c r="D13" s="124" t="str">
-        <x:v>Run with --offline to reproduce from cached sources.</x:v>
+    <x:row r="13" ht="24" hidden="0" customHeight="1">
+      <x:c r="A13" s="123" t="str">
+        <x:v>Zenodo version 1.0.1 archive</x:v>
+      </x:c>
+      <x:c r="B13" s="123" t="str">
+        <x:v>Independent timestamp for the frozen specification</x:v>
+      </x:c>
+      <x:c r="C13" s="123" t="str">
+        <x:v>https://doi.org/10.5281/zenodo.23246551</x:v>
+      </x:c>
+      <x:c r="D13" s="123" t="str">
+        <x:v>Published October 8, 2026, before the planned historical and prospective tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
@@ -14051,7 +14004,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2abb03029fd4d15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa690ddc36ef4727"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14262,7 +14215,7 @@
     </x:row>
     <x:row r="17" ht="42" hidden="0" customHeight="1">
       <x:c r="A17" s="113" t="str">
-        <x:v>The trigger and weights were selected after reviewing 2023. The result is in-sample, has an 80% false-positive share among top-decile flags, and does not establish causation or out-of-sample predictive accuracy. The method must be frozen before the planned 2008-2011 test.</x:v>
+        <x:v>The trigger and weights were selected after reviewing 2023. The result is in-sample, has an 80% false-positive share among top-decile flags, and does not establish causation or predictive accuracy. The unchanged specification was frozen and independently timestamped as version 1.0.1 on October 8, 2026 (https://doi.org/10.5281/zenodo.23246551) before the planned historical holdout and prospective tests.</x:v>
       </x:c>
       <x:c r="B17" s="113" t="str">
         <x:v>The trigger and weights were selected after reviewing 2023. The result is in-sample, has an 80% false-positive share among top-decile flags, and does not establish causation or out-of-sample predictive accuracy. The method must be frozen before the planned 2008-2011 test.</x:v>
@@ -15390,27 +15343,27 @@
         <x:v>Target date</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="66" hidden="0" customHeight="1">
-      <x:c r="A5" s="81" t="str">
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
+      <x:c r="A5" s="128" t="str">
         <x:v>T1</x:v>
       </x:c>
-      <x:c r="B5" s="81" t="str">
-        <x:v>Freeze specification</x:v>
-      </x:c>
-      <x:c r="C5" s="81" t="str">
-        <x:v>Fix variables, missing-data rules, weights, trigger, and sample construction as version 1.0. Publish before running T2-T5.</x:v>
-      </x:c>
-      <x:c r="D5" s="81" t="str">
+      <x:c r="B5" s="128" t="str">
+        <x:v>Freeze specification - completed</x:v>
+      </x:c>
+      <x:c r="C5" s="128" t="str">
+        <x:v>Version 1.0.1 fixed the variables, missing-data rules, weights, trigger, and sample construction before any new test was run.</x:v>
+      </x:c>
+      <x:c r="D5" s="128" t="str">
         <x:v>Public dated specification</x:v>
       </x:c>
-      <x:c r="E5" s="81" t="str">
-        <x:v>Archived specification with a DOI or equivalent independent timestamp before any new test</x:v>
-      </x:c>
-      <x:c r="F5" s="81" t="str">
-        <x:v>Q1 2027</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="66" hidden="0" customHeight="1">
+      <x:c r="E5" s="128" t="str">
+        <x:v>Completed. Version 1.0.1 was archived on October 8, 2026 at doi:10.5281/zenodo.23246551.</x:v>
+      </x:c>
+      <x:c r="F5" s="128" t="str">
+        <x:v>Completed October 8, 2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
       <x:c r="A6" s="81" t="str">
         <x:v>T2</x:v>
       </x:c>
@@ -15430,15 +15383,15 @@
         <x:v>Q2 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="66" hidden="0" customHeight="1">
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
       <x:c r="A7" s="81" t="str">
         <x:v>T3</x:v>
       </x:c>
       <x:c r="B7" s="81" t="str">
-        <x:v>Out-of-episode test: 2008-2011</x:v>
+        <x:v>Historical holdout: 2008-2011</x:v>
       </x:c>
       <x:c r="C7" s="81" t="str">
-        <x:v>Apply frozen version 1.0 unchanged to pre-crisis Call Report data. Outcome is failure in the following eight quarters.</x:v>
+        <x:v>Apply frozen version 1.0.1 unchanged to pre-crisis Call Report data. Outcome is FDIC failure in the following eight quarters.</x:v>
       </x:c>
       <x:c r="D7" s="81" t="str">
         <x:v>AUC, capture, precision, calibration</x:v>
@@ -15450,111 +15403,141 @@
         <x:v>Q3 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="66" hidden="0" customHeight="1">
+    <x:row r="8" ht="150" hidden="0" customHeight="1">
       <x:c r="A8" s="81" t="str">
         <x:v>T4</x:v>
       </x:c>
       <x:c r="B8" s="81" t="str">
-        <x:v>Cross-episode robustness</x:v>
+        <x:v>Historical holdout: 2019-2020</x:v>
       </x:c>
       <x:c r="C8" s="81" t="str">
-        <x:v>Compare the integrated score with each single ratio and a simple ratio screen across the 2008-2011 test and the 2023 diagnostic.</x:v>
+        <x:v>Primary test: apply frozen version 1.0.1 unchanged to a single 2019Q4 baseline and follow each bank for four quarters through 2020Q4. Secondary robustness test: rolling 2019Q1-2019Q4 baselines, each followed for four quarters. Outcome, measured over the same four-quarter window for every component: FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. An eight-quarter failure analysis may be reported separately as a secondary endpoint. Any results from 2020 baselines are labeled contemporaneous monitoring, not pre-stress prediction.</x:v>
       </x:c>
       <x:c r="D8" s="81" t="str">
-        <x:v>Worst-episode AUC per signal</x:v>
+        <x:v>AUC, top-decile capture and precision; bank-clustered confidence intervals for the rolling secondary test</x:v>
       </x:c>
       <x:c r="E8" s="81" t="str">
-        <x:v>Highest worst-episode AUC and no episode more than 0.02 below the best benchmark</x:v>
+        <x:v>Primary test passes only if AUC is at least 0.70, at least 0.03 above the best single-ratio AUC, and top-decile precision is at least 5 percentage points above the best single ratio. Secondary, eight-quarter, and monitoring results are reported but do not determine pass or fail.</x:v>
       </x:c>
       <x:c r="F8" s="81" t="str">
         <x:v>Q4 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="66" hidden="0" customHeight="1">
+    <x:row r="9" ht="105" hidden="0" customHeight="1">
       <x:c r="A9" s="81" t="str">
         <x:v>T5</x:v>
       </x:c>
       <x:c r="B9" s="81" t="str">
-        <x:v>False-positive burden</x:v>
+        <x:v>Prospective validation</x:v>
       </x:c>
       <x:c r="C9" s="81" t="str">
-        <x:v>Measure precision at fixed top-decile and top-quintile cutoffs and document stressed survivors and ordinary survivors.</x:v>
+        <x:v>Apply frozen version 1.0.1 unchanged to a single 2026Q3 baseline, the first quarter whose Call Report data were not available when version 1.0.1 was frozen. Follow each eligible bank for eight quarters through 2028Q3. Outcome over that eight-quarter window: FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. Do not retune after results become available.</x:v>
       </x:c>
       <x:c r="D9" s="81" t="str">
-        <x:v>Precision, false-positive share, review volume</x:v>
+        <x:v>AUC, top-decile capture and precision, confidence intervals</x:v>
       </x:c>
       <x:c r="E9" s="81" t="str">
-        <x:v>Report all results. The integrated score must improve precision by at least 5 percentage points over the best single ratio to claim operational advantage</x:v>
+        <x:v>Same pass marks as the T4 primary test. If fewer than five outcome banks occur, classify the test as inconclusive and continue observation without retuning.</x:v>
       </x:c>
       <x:c r="F9" s="81" t="str">
-        <x:v>Q4 2027</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="66" hidden="0" customHeight="1">
+        <x:v>Q1 2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
       <x:c r="A10" s="81" t="str">
         <x:v>T6</x:v>
       </x:c>
       <x:c r="B10" s="81" t="str">
+        <x:v>Cross-episode robustness</x:v>
+      </x:c>
+      <x:c r="C10" s="81" t="str">
+        <x:v>Compare the integrated score with each single ratio and a simple ratio screen across T3-T5 and the 2023 development diagnostic.</x:v>
+      </x:c>
+      <x:c r="D10" s="81" t="str">
+        <x:v>Worst-episode AUC per signal</x:v>
+      </x:c>
+      <x:c r="E10" s="81" t="str">
+        <x:v>Highest worst-episode AUC and no episode more than 0.02 below the best benchmark</x:v>
+      </x:c>
+      <x:c r="F10" s="81" t="str">
+        <x:v>Q1 2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
+      <x:c r="A11" s="81" t="str">
+        <x:v>T7</x:v>
+      </x:c>
+      <x:c r="B11" s="81" t="str">
+        <x:v>False-positive burden</x:v>
+      </x:c>
+      <x:c r="C11" s="81" t="str">
+        <x:v>Measure precision at fixed top-decile and top-quintile cutoffs and document stressed survivors and ordinary survivors.</x:v>
+      </x:c>
+      <x:c r="D11" s="81" t="str">
+        <x:v>Precision, false-positive share, review volume</x:v>
+      </x:c>
+      <x:c r="E11" s="81" t="str">
+        <x:v>Report all results. The integrated score must improve precision by at least 5 percentage points over the best single ratio to claim operational advantage</x:v>
+      </x:c>
+      <x:c r="F11" s="81" t="str">
+        <x:v>Q1 2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
+      <x:c r="A12" s="81" t="str">
+        <x:v>T8</x:v>
+      </x:c>
+      <x:c r="B12" s="81" t="str">
         <x:v>Smaller banks</x:v>
       </x:c>
-      <x:c r="C10" s="81" t="str">
+      <x:c r="C12" s="81" t="str">
         <x:v>Extend the frozen method from $10bn-$250bn banks to $1bn-$10bn banks without retuning.</x:v>
       </x:c>
-      <x:c r="D10" s="81" t="str">
-        <x:v>Same metrics as T3-T5</x:v>
-      </x:c>
-      <x:c r="E10" s="81" t="str">
+      <x:c r="D12" s="81" t="str">
+        <x:v>Same metrics as T3-T7</x:v>
+      </x:c>
+      <x:c r="E12" s="81" t="str">
         <x:v>AUC no more than 0.05 below performance in the primary size band</x:v>
       </x:c>
-      <x:c r="F10" s="81" t="str">
-        <x:v>Q2 2028</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="66" hidden="0" customHeight="1">
-      <x:c r="A11" s="83" t="str">
-        <x:v>T7</x:v>
-      </x:c>
-      <x:c r="B11" s="83" t="str">
+      <x:c r="F12" s="81" t="str">
+        <x:v>Q2 2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="36" hidden="0" customHeight="1">
+      <x:c r="A13" s="81" t="str">
+        <x:v>T9</x:v>
+      </x:c>
+      <x:c r="B13" s="81" t="str">
         <x:v>Benchmark published approaches</x:v>
       </x:c>
-      <x:c r="C11" s="83" t="str">
+      <x:c r="C13" s="81" t="str">
         <x:v>Compare with public Federal Reserve and supervisory methodology documents where the inputs and outcomes are comparable.</x:v>
       </x:c>
-      <x:c r="D11" s="83" t="str">
+      <x:c r="D13" s="81" t="str">
         <x:v>Qualitative mapping and rank comparison</x:v>
       </x:c>
-      <x:c r="E11" s="83" t="str">
+      <x:c r="E13" s="81" t="str">
         <x:v>Documented differences, limitations, and complementary uses; no unsupported superiority claim</x:v>
       </x:c>
-      <x:c r="F11" s="83" t="str">
-        <x:v>Q4 2028</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" hidden="0" customHeight="1">
-      <x:c r="A13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
-      <x:c r="B13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
-      <x:c r="C13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
-      <x:c r="D13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
-      <x:c r="E13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
-      <x:c r="F13" s="29" t="str">
-        <x:v>A failed test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
-      </x:c>
+      <x:c r="F13" s="81" t="str">
+        <x:v>Q4 2029</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="25.5" customHeight="1">
+      <x:c r="A15" s="131" t="str">
+        <x:v>A failed or inconclusive test will be reported. The integrated method will not be described as superior unless it meets the frozen, quantitative criteria.</x:v>
+      </x:c>
+      <x:c r="B15" s="131"/>
+      <x:c r="C15" s="131"/>
+      <x:c r="D15" s="131"/>
+      <x:c r="E15" s="131"/>
+      <x:c r="F15" s="131"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
-    <x:mergeCell ref="A13:F13"/>
+    <x:mergeCell ref="A15:F15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -15611,201 +15594,201 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A5" s="7" t="str">
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
+      <x:c r="A5" s="77" t="str">
         <x:v>0. Set-up</x:v>
       </x:c>
-      <x:c r="B5" s="7" t="str">
+      <x:c r="B5" s="77" t="str">
         <x:v>Q4 2026</x:v>
       </x:c>
-      <x:c r="C5" s="7" t="str">
+      <x:c r="C5" s="77" t="str">
         <x:v>Correct peer filter; recompute scores; disclose false positives; anonymize filed workbook; archive code and raw data</x:v>
       </x:c>
-      <x:c r="D5" s="7" t="str">
+      <x:c r="D5" s="77" t="str">
         <x:v>Corrected workbook and reproducibility package</x:v>
       </x:c>
-      <x:c r="E5" s="7" t="str">
+      <x:c r="E5" s="77" t="str">
         <x:v>Workbook formulas; code; raw sources; checksum manifest</x:v>
       </x:c>
-      <x:c r="F5" s="121" t="str">
+      <x:c r="F5" s="133" t="str">
         <x:v>Completed</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A6" s="7" t="str">
+    <x:row r="6" ht="24" hidden="0" customHeight="1">
+      <x:c r="A6" s="77" t="str">
         <x:v>0. Set-up</x:v>
       </x:c>
-      <x:c r="B6" s="7" t="str">
+      <x:c r="B6" s="77" t="str">
         <x:v>Q4 2026</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="str">
+      <x:c r="C6" s="77" t="str">
         <x:v>Confirm personal-time separation and any required outside-activity approval</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="str">
+      <x:c r="D6" s="77" t="str">
         <x:v>Written confirmation or approval record</x:v>
       </x:c>
-      <x:c r="E6" s="7" t="str">
+      <x:c r="E6" s="77" t="str">
         <x:v>Dated note or employer approval, if required</x:v>
       </x:c>
-      <x:c r="F6" s="121" t="str">
+      <x:c r="F6" s="132" t="str">
         <x:v>User action required</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A7" s="7" t="s">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="77" t="str">
+        <x:v>1. Validate</x:v>
+      </x:c>
+      <x:c r="B7" s="77" t="str">
+        <x:v>October 8, 2026</x:v>
+      </x:c>
+      <x:c r="C7" s="77" t="str">
+        <x:v>Freeze and publish version 1.0.1 specification</x:v>
+      </x:c>
+      <x:c r="D7" s="77" t="str">
+        <x:v>Public frozen specification</x:v>
+      </x:c>
+      <x:c r="E7" s="77" t="str">
+        <x:v>doi:10.5281/zenodo.23246551</x:v>
+      </x:c>
+      <x:c r="F7" s="133" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" hidden="0" customHeight="1">
+      <x:c r="A8" s="77" t="str">
+        <x:v>1. Validate</x:v>
+      </x:c>
+      <x:c r="B8" s="77" t="str">
+        <x:v>Q1 to Q2 2027</x:v>
+      </x:c>
+      <x:c r="C8" s="77" t="str">
+        <x:v>Build quarterly bank panel (2001 to latest) from Call Reports; add FRED macro series</x:v>
+      </x:c>
+      <x:c r="D8" s="77" t="str">
+        <x:v>Reproducible data pipeline</x:v>
+      </x:c>
+      <x:c r="E8" s="77" t="str">
+        <x:v>Repository release</x:v>
+      </x:c>
+      <x:c r="F8" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="77" t="str">
+        <x:v>1. Validate</x:v>
+      </x:c>
+      <x:c r="B9" s="77" t="str">
+        <x:v>Q2 to Q4 2027</x:v>
+      </x:c>
+      <x:c r="C9" s="77" t="str">
+        <x:v>Run T2-T4 and initial T6-T7 analyses without retuning</x:v>
+      </x:c>
+      <x:c r="D9" s="77" t="str">
+        <x:v>Historical validation results report</x:v>
+      </x:c>
+      <x:c r="E9" s="77" t="str">
+        <x:v>Public report with all results, including failures and inconclusive tests</x:v>
+      </x:c>
+      <x:c r="F9" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
+      <x:c r="A10" s="77" t="str">
+        <x:v>1. Validate</x:v>
+      </x:c>
+      <x:c r="B10" s="77" t="str">
+        <x:v>Q4 2028 to Q1 2029</x:v>
+      </x:c>
+      <x:c r="C10" s="77" t="str">
+        <x:v>Complete the prospective T5 outcome window (2026Q3 baseline through 2028Q3); update T6-T7</x:v>
+      </x:c>
+      <x:c r="D10" s="77" t="str">
+        <x:v>Prospective validation report</x:v>
+      </x:c>
+      <x:c r="E10" s="77" t="str">
+        <x:v>Dated public report using the frozen specification</x:v>
+      </x:c>
+      <x:c r="F10" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
+      <x:c r="A11" s="77" t="str">
+        <x:v>2. Share findings</x:v>
+      </x:c>
+      <x:c r="B11" s="77" t="str">
+        <x:v>Q3 2027</x:v>
+      </x:c>
+      <x:c r="C11" s="77" t="str">
+        <x:v>Working paper</x:v>
+      </x:c>
+      <x:c r="D11" s="77" t="str">
+        <x:v>Paper posted on SSRN</x:v>
+      </x:c>
+      <x:c r="E11" s="77" t="str">
+        <x:v>SSRN posting date and download count</x:v>
+      </x:c>
+      <x:c r="F11" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" hidden="0" customHeight="1">
+      <x:c r="A12" s="77" t="str">
+        <x:v>2. Share findings</x:v>
+      </x:c>
+      <x:c r="B12" s="77" t="str">
+        <x:v>Q4 2027 to Q2 2029</x:v>
+      </x:c>
+      <x:c r="C12" s="77" t="str">
+        <x:v>Present to practitioners and researchers</x:v>
+      </x:c>
+      <x:c r="D12" s="77" t="str">
+        <x:v>Talks, e.g., GARP chapter, a state bankers association, the Federal Reserve and CSBS Community Banking research conference</x:v>
+      </x:c>
+      <x:c r="E12" s="77" t="str">
+        <x:v>Invitations, programs, attendee counts</x:v>
+      </x:c>
+      <x:c r="F12" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" hidden="0" customHeight="1">
+      <x:c r="A13" s="77" t="str">
+        <x:v>2. Share findings</x:v>
+      </x:c>
+      <x:c r="B13" s="77" t="str">
+        <x:v>Q2 2029</x:v>
+      </x:c>
+      <x:c r="C13" s="77" t="str">
+        <x:v>Submit updated evidence to a peer-reviewed journal</x:v>
+      </x:c>
+      <x:c r="D13" s="77" t="str">
+        <x:v>Journal submission including historical and prospective results</x:v>
+      </x:c>
+      <x:c r="E13" s="77" t="str">
+        <x:v>Submission confirmation; reviewer feedback</x:v>
+      </x:c>
+      <x:c r="F13" s="132" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" hidden="0" customHeight="1">
+      <x:c r="A14" s="7" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E7" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F7" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A8" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E8" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F8" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A9" s="7" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E9" s="7" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F9" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A10" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="C10" s="7" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E10" s="7" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F10" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A11" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F11" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A12" s="7" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D12" s="7" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E12" s="7" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F12" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A13" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B13" s="7" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E13" s="7" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F13" s="30" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="43.5" hidden="0" customHeight="1">
-      <x:c r="A14" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B14" s="7" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="s">
-        <x:v>73</x:v>
+      <x:c r="B14" s="7" t="str">
+        <x:v>Q4 2028 to Q2 2029</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>Publish validation protocol aligned with model risk management guidance (SR 11-7); release a bank self-assessment template; extend the frozen method to $1bn-$10bn banks (T8)</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
+        <x:v>Protocol document; Excel and Python self-assessment template with user guide; T8 results</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="str">
+        <x:v>Public releases; downloads; feedback from banks</x:v>
       </x:c>
       <x:c r="F14" s="30" t="s">
         <x:v>43</x:v>
@@ -15813,19 +15796,19 @@
     </x:row>
     <x:row r="15" ht="43.5" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="7" t="s">
-        <x:v>75</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="7" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F15" s="30" t="s">
         <x:v>43</x:v>
@@ -15833,19 +15816,19 @@
     </x:row>
     <x:row r="16" ht="43.5" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="s">
-        <x:v>80</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="str">
+        <x:v>Refresh with each year-end Call Report cycle; compare with published Federal Reserve models (T9)</x:v>
       </x:c>
       <x:c r="D16" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E16" s="7" t="s">
-        <x:v>82</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F16" s="30" t="s">
         <x:v>43</x:v>
@@ -15853,7 +15836,7 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="31" t="s">
-        <x:v>83</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="31"/>
       <x:c r="C18" s="31"/>
@@ -15884,7 +15867,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>84</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -15904,7 +15887,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>85</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -16129,7 +16112,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd21ba86f97ca4c99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03645c606444e18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16488,9 +16471,9 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5a5adfb5f564eeb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R031691513b22431f"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0be2cdd4c0e4d06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R830671f861fc469b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16509,7 +16492,7 @@
   <x:sheetData>
     <x:row r="1" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>86</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B1" s="9"/>
       <x:c r="C1" s="9"/>
@@ -16520,7 +16503,7 @@
     </x:row>
     <x:row r="2" ht="33.75" hidden="0" customHeight="1">
       <x:c r="A2" s="10" t="s">
-        <x:v>87</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="10"/>
       <x:c r="C2" s="10"/>
@@ -16927,7 +16910,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2c122c79d804bc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40fec28c294544be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/call_report_preliminary_analysis.xlsx
+++ b/call_report_preliminary_analysis.xlsx
@@ -15383,7 +15383,7 @@
         <x:v>Q2 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="36" hidden="0" customHeight="1">
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
       <x:c r="A7" s="81" t="str">
         <x:v>T3</x:v>
       </x:c>
@@ -15391,7 +15391,7 @@
         <x:v>Historical holdout: 2008-2011</x:v>
       </x:c>
       <x:c r="C7" s="81" t="str">
-        <x:v>Apply frozen version 1.0.1 unchanged to pre-crisis Call Report data. Outcome is FDIC failure in the following eight quarters.</x:v>
+        <x:v>Apply frozen version 1.0.1 unchanged to a single 2007Q4 baseline. Outcome is FDIC failure in the following eight quarters (2008Q1-2009Q4). Operational rules R1-R8 apply.</x:v>
       </x:c>
       <x:c r="D7" s="81" t="str">
         <x:v>AUC, capture, precision, calibration</x:v>
@@ -15403,7 +15403,7 @@
         <x:v>Q3 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="150" hidden="0" customHeight="1">
+    <x:row r="8" ht="190" hidden="0" customHeight="1">
       <x:c r="A8" s="81" t="str">
         <x:v>T4</x:v>
       </x:c>
@@ -15411,19 +15411,19 @@
         <x:v>Historical holdout: 2019-2020</x:v>
       </x:c>
       <x:c r="C8" s="81" t="str">
-        <x:v>Primary test: apply frozen version 1.0.1 unchanged to a single 2019Q4 baseline and follow each bank for four quarters through 2020Q4. Secondary robustness test: rolling 2019Q1-2019Q4 baselines, each followed for four quarters. Outcome, measured over the same four-quarter window for every component: FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. An eight-quarter failure analysis may be reported separately as a secondary endpoint. Any results from 2020 baselines are labeled contemporaneous monitoring, not pre-stress prediction.</x:v>
+        <x:v>Primary test: apply frozen version 1.0.1 unchanged to a single 2019Q4 baseline and follow each bank for four quarters through 2020Q4. Secondary robustness test: rolling 2019Q1-2019Q4 baselines, each followed for four quarters. Outcome, measured over the same four-quarter window for every component and at the worst quarter in that window (rule R4): FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. An eight-quarter failure analysis may be reported separately as a secondary endpoint. Any results from 2020 baselines are labeled contemporaneous monitoring, not pre-stress prediction. No bank-level 2019-2020 test results were calculated or inspected before the v1.0.2 test definition and pass criteria were publicly timestamped.</x:v>
       </x:c>
       <x:c r="D8" s="81" t="str">
         <x:v>AUC, top-decile capture and precision; bank-clustered confidence intervals for the rolling secondary test</x:v>
       </x:c>
       <x:c r="E8" s="81" t="str">
-        <x:v>Primary test passes only if AUC is at least 0.70, at least 0.03 above the best single-ratio AUC, and top-decile precision is at least 5 percentage points above the best single ratio. Secondary, eight-quarter, and monitoring results are reported but do not determine pass or fail.</x:v>
+        <x:v>Primary test passes only if AUC is at least 0.70, at least 0.03 above the best single-ratio AUC, and top-decile precision is at least 5 percentage points above the best single ratio. Inconclusive if the primary cohort has fewer than five outcome banks (R6). Secondary, eight-quarter, and monitoring results are reported but do not determine pass or fail.</x:v>
       </x:c>
       <x:c r="F8" s="81" t="str">
         <x:v>Q4 2027</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="105" hidden="0" customHeight="1">
+    <x:row r="9" ht="115" hidden="0" customHeight="1">
       <x:c r="A9" s="81" t="str">
         <x:v>T5</x:v>
       </x:c>
@@ -15431,7 +15431,7 @@
         <x:v>Prospective validation</x:v>
       </x:c>
       <x:c r="C9" s="81" t="str">
-        <x:v>Apply frozen version 1.0.1 unchanged to a single 2026Q3 baseline, the first quarter whose Call Report data were not available when version 1.0.1 was frozen. Follow each eligible bank for eight quarters through 2028Q3. Outcome over that eight-quarter window: FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. Do not retune after results become available.</x:v>
+        <x:v>Apply frozen version 1.0.1 unchanged to a single 2026Q3 baseline, the first quarter whose Call Report data were not available when version 1.0.1 was frozen. Follow each eligible bank for eight quarters through 2028Q3. Outcome over that eight-quarter window, measured at the worst quarter (rule R4): FDIC failure, a decline in equity-to-assets of at least 2 percentage points, or an increase in noncurrent loans-to-gross loans of at least 1 percentage point that also reaches 2%. Do not retune after results become available.</x:v>
       </x:c>
       <x:c r="D9" s="81" t="str">
         <x:v>AUC, top-decile capture and precision, confidence intervals</x:v>
@@ -15533,11 +15533,146 @@
       <x:c r="E15" s="131"/>
       <x:c r="F15" s="131"/>
     </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="72" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B17" s="73" t="str">
+        <x:v>Operational rule (added in v1.0.3, before any test was run)</x:v>
+      </x:c>
+      <x:c r="C17" s="73" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+      <x:c r="D17" s="73"/>
+      <x:c r="E17" s="73"/>
+      <x:c r="F17" s="76"/>
+    </x:row>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="81" t="str">
+        <x:v>R1</x:v>
+      </x:c>
+      <x:c r="B18" s="81" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="C18" s="81" t="str">
+        <x:v>These rules apply to T3, T4, and T5. They were added in version 1.0.3, before any of those tests was run, and do not change the indicators, percentile construction, weights, interaction term, or dominant-risk trigger frozen in version 1.0.1.</x:v>
+      </x:c>
+      <x:c r="D18" s="81"/>
+      <x:c r="E18" s="81"/>
+      <x:c r="F18" s="81"/>
+    </x:row>
+    <x:row r="19" ht="45" customHeight="1">
+      <x:c r="A19" s="81" t="str">
+        <x:v>R2</x:v>
+      </x:c>
+      <x:c r="B19" s="81" t="str">
+        <x:v>Eligibility</x:v>
+      </x:c>
+      <x:c r="C19" s="81" t="str">
+        <x:v>A bank is eligible if its baseline-quarter Call Report shows total assets of $10 billion to $250 billion and complete trigger inputs. Eligibility is fixed at the baseline: a bank that later moves outside the asset band stays in the cohort.</x:v>
+      </x:c>
+      <x:c r="D19" s="81"/>
+      <x:c r="E19" s="81"/>
+      <x:c r="F19" s="81"/>
+    </x:row>
+    <x:row r="20" ht="45" customHeight="1">
+      <x:c r="A20" s="81" t="str">
+        <x:v>R3</x:v>
+      </x:c>
+      <x:c r="B20" s="81" t="str">
+        <x:v>Failure</x:v>
+      </x:c>
+      <x:c r="C20" s="81" t="str">
+        <x:v>A bank counts as a failure if it appears on the FDIC failed-bank list with a closing date inside the outcome window, including FDIC-assisted transactions. A failure counts as an outcome regardless of any other data.</x:v>
+      </x:c>
+      <x:c r="D20" s="81"/>
+      <x:c r="E20" s="81"/>
+      <x:c r="F20" s="81"/>
+    </x:row>
+    <x:row r="21" ht="90" customHeight="1">
+      <x:c r="A21" s="81" t="str">
+        <x:v>R4</x:v>
+      </x:c>
+      <x:c r="B21" s="81" t="str">
+        <x:v>Capital and credit deterioration</x:v>
+      </x:c>
+      <x:c r="C21" s="81" t="str">
+        <x:v>Measured at the worst quarter in the outcome window, not the final quarter. Capital deterioration: the lowest equity-to-assets ratio reported in any window quarter is at least 2 percentage points below the baseline ratio. Credit deterioration: the highest noncurrent loans-to-gross loans ratio reported in any window quarter is at least 1 percentage point above the baseline ratio and at least 2%. Where a test's outcome includes these components, an outcome occurs if failure, capital deterioration, or credit deterioration occurs.</x:v>
+      </x:c>
+      <x:c r="D21" s="81"/>
+      <x:c r="E21" s="81"/>
+      <x:c r="F21" s="81"/>
+    </x:row>
+    <x:row r="22" ht="75" customHeight="1">
+      <x:c r="A22" s="81" t="str">
+        <x:v>R5</x:v>
+      </x:c>
+      <x:c r="B22" s="81" t="str">
+        <x:v>Mergers, exits, and missing reports</x:v>
+      </x:c>
+      <x:c r="C22" s="81" t="str">
+        <x:v>A bank that stops filing during the window without failing (for example, because it was acquired or merged) is assessed on the window quarters it did report. Missing quarters are skipped. A bank with no Call Report in the outcome window is excluded from the primary analysis and listed in the results. A sensitivity analysis that excludes every bank exiting before the window ends is reported separately.</x:v>
+      </x:c>
+      <x:c r="D22" s="81"/>
+      <x:c r="E22" s="81"/>
+      <x:c r="F22" s="81"/>
+    </x:row>
+    <x:row r="23" ht="45" customHeight="1">
+      <x:c r="A23" s="81" t="str">
+        <x:v>R6</x:v>
+      </x:c>
+      <x:c r="B23" s="81" t="str">
+        <x:v>Inconclusive results</x:v>
+      </x:c>
+      <x:c r="C23" s="81" t="str">
+        <x:v>A test whose primary cohort has fewer than five outcome banks is reported as inconclusive. T5 then continues prospective observation without retuning; T3 and T4 results are reported descriptively.</x:v>
+      </x:c>
+      <x:c r="D23" s="81"/>
+      <x:c r="E23" s="81"/>
+      <x:c r="F23" s="81"/>
+    </x:row>
+    <x:row r="24" ht="75" customHeight="1">
+      <x:c r="A24" s="81" t="str">
+        <x:v>R7</x:v>
+      </x:c>
+      <x:c r="B24" s="81" t="str">
+        <x:v>Confidence intervals</x:v>
+      </x:c>
+      <x:c r="C24" s="81" t="str">
+        <x:v>For single-baseline cohorts (T3, T4 primary, T5): 95% confidence intervals for AUC by the DeLong method, and for top-decile capture and precision by a bank-level bootstrap with 2,000 resamples. For the rolling T4 secondary cohort: a bank-clustered bootstrap with 2,000 resamples. Pass or fail is judged on point estimates against the pre-stated criteria; intervals are reported alongside.</x:v>
+      </x:c>
+      <x:c r="D24" s="81"/>
+      <x:c r="E24" s="81"/>
+      <x:c r="F24" s="81"/>
+    </x:row>
+    <x:row r="25" ht="45" customHeight="1">
+      <x:c r="A25" s="81" t="str">
+        <x:v>R8</x:v>
+      </x:c>
+      <x:c r="B25" s="81" t="str">
+        <x:v>Data provenance</x:v>
+      </x:c>
+      <x:c r="C25" s="81" t="str">
+        <x:v>Call Report and failure data are downloaded from public FFIEC or FDIC sources when each test is run. Download dates and SHA-256 hashes of the raw files are published with the results.</x:v>
+      </x:c>
+      <x:c r="D25" s="81"/>
+      <x:c r="E25" s="81"/>
+      <x:c r="F25" s="81"/>
+    </x:row>
   </x:sheetData>
-  <x:mergeCells>
+  <x:mergeCells count="12">
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A15:F15"/>
+    <x:mergeCell ref="C17:F17"/>
+    <x:mergeCell ref="C18:F18"/>
+    <x:mergeCell ref="C19:F19"/>
+    <x:mergeCell ref="C20:F20"/>
+    <x:mergeCell ref="C21:F21"/>
+    <x:mergeCell ref="C22:F22"/>
+    <x:mergeCell ref="C23:F23"/>
+    <x:mergeCell ref="C24:F24"/>
+    <x:mergeCell ref="C25:F25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/call_report_preliminary_analysis.xlsx
+++ b/call_report_preliminary_analysis.xlsx
@@ -3449,7 +3449,7 @@
         <x:v>A testable next step</x:v>
       </x:c>
       <x:c r="B11" s="77" t="str">
-        <x:v>Version 1.0.1 was frozen and independently timestamped on October 8, 2026 (https://doi.org/10.5281/zenodo.23246551). The unchanged specification will be evaluated in the 2008-2011 and 2019-2020 historical tests and in a prospective test.</x:v>
+        <x:v>Version 1.0.1 was frozen and independently timestamped on October 8, 2026 (https://doi.org/10.5281/zenodo.23246551). The unchanged specification will be evaluated in the 2008-2009 and 2019-2020 historical tests and in a prospective test.</x:v>
       </x:c>
       <x:c r="C11" s="77" t="str">
         <x:v>See Validation Roadmap and Milestones.</x:v>
@@ -15196,7 +15196,7 @@
         <x:v>The integrated score and uninsured-deposit ratio each capture all three failures in the top 15.</x:v>
       </x:c>
       <x:c r="D6" s="81" t="str">
-        <x:v>Open research question. Test 2008-2011 without changing version 1.0.</x:v>
+        <x:v>Open research question. Test 2008-2009 failures from a 2007Q4 baseline without changing version 1.0.1.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="72" hidden="0" customHeight="1">
@@ -15388,7 +15388,7 @@
         <x:v>T3</x:v>
       </x:c>
       <x:c r="B7" s="81" t="str">
-        <x:v>Historical holdout: 2008-2011</x:v>
+        <x:v>Historical holdout: 2008-2009</x:v>
       </x:c>
       <x:c r="C7" s="81" t="str">
         <x:v>Apply frozen version 1.0.1 unchanged to a single 2007Q4 baseline. Outcome is FDIC failure in the following eight quarters (2008Q1-2009Q4). Operational rules R1-R8 apply.</x:v>
